--- a/artfynd/A 1561-2023 artfynd.xlsx
+++ b/artfynd/A 1561-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1561-2023 artfynd.xlsx
+++ b/artfynd/A 1561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,40 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106665154</v>
+        <v>106668001</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663999.8584187516</v>
+        <v>664027</v>
       </c>
       <c r="R2" t="n">
-        <v>6526471.70461249</v>
+        <v>6526525</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,49 +792,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106668001</v>
+        <v>106665154</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664026.1339586312</v>
+        <v>663999</v>
       </c>
       <c r="R3" t="n">
-        <v>6526525.148791636</v>
+        <v>6526472</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107546419</v>
+        <v>106670788</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664013.0306233913</v>
+        <v>664045</v>
       </c>
       <c r="R4" t="n">
-        <v>6526467.083342727</v>
+        <v>6526519</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,22 +966,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,6 +1005,224 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107546419</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>664013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6526467</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127503315</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>663960</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6526461</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1561-2023 artfynd.xlsx
+++ b/artfynd/A 1561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106668001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106665154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106670788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107546419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,8 +1248,20 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127503315</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>